--- a/docs/CUE_REVIEW_2026-07-23.xlsx
+++ b/docs/CUE_REVIEW_2026-07-23.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LFA Exercise Cue Review — Sam's sign-off pass (2026-07-23)</t>
+          <t>LFA Exercise Cue Review — Sam's sign-off pass (2026-07-23) [NON-CANONICAL — HISTORICAL POINTER ONLY, 2026-07-28] This workbook is NOT a source of truth and no gate reads it. Its rewrite columns F/G are BLANK on all 143 exercise rows — Sam's edited copy was never committed; his rulings were transcribed into docs/CUE_CHANGESET_2026-07-23.md. The cue source is docs/EXERCISE_MASTER_SHEET_2026-07-28.xlsx.</t>
         </is>
       </c>
     </row>
